--- a/artfynd/A 24681-2023 artfynd.xlsx
+++ b/artfynd/A 24681-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121395906</v>
       </c>
       <c r="B2" t="n">
-        <v>78246</v>
+        <v>78249</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 24681-2023 artfynd.xlsx
+++ b/artfynd/A 24681-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121395906</v>
       </c>
       <c r="B2" t="n">
-        <v>78249</v>
+        <v>78252</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 24681-2023 artfynd.xlsx
+++ b/artfynd/A 24681-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121395906</v>
       </c>
       <c r="B2" t="n">
-        <v>78252</v>
+        <v>78253</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 24681-2023 artfynd.xlsx
+++ b/artfynd/A 24681-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121395906</v>
       </c>
       <c r="B2" t="n">
-        <v>78253</v>
+        <v>78254</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 24681-2023 artfynd.xlsx
+++ b/artfynd/A 24681-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121395906</v>
       </c>
       <c r="B2" t="n">
-        <v>78254</v>
+        <v>78261</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
